--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA151"/>
+  <dimension ref="A1:AA155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16260,6 +16260,382 @@
       <c r="Z151" s="2" t="inlineStr"/>
       <c r="AA151" s="2" t="inlineStr"/>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Thirsty Scholar</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Thirsty Scholar</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>55003</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Taichung</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Taichung City, West District</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>172 Cunzhong Street</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>retail@thirsty-scholar.net</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>+886 4 2378 7546</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>42945705</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr"/>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thirstysc/</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thirsty_scholar_tw/</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr"/>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Danny Wine Collection Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Danny Wine Collection Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>55032</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>No. 22, Lane 69, Section 2, Jianguo South Road, Daan District</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dannycollection.com</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>dwc.taipei@gmail.com</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2708 8869</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>24755055</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr"/>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DannyWine</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dwc_taipei/</t>
+        </is>
+      </c>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr"/>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Wine O'clock Company Limited</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Wine O'clock Company Limited</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>55010</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>3 Yijiang Street</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>taiwan@wineoclock.com.tw</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2521 1860</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>82863813</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr"/>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineOClockTaiwan/</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr"/>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Topcollection E.n. Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Topcollection E.n. Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>121872</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Kaohsiung</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Kaohsiung City, Gushan District</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>88 Meishu East 8th Street</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>topcollectionwine@gmail.com</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>+886 7 552 9782</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>59172984</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr"/>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Topcollection.wine/</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>Nicole Hu</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicole-hu-aa5929159/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA155"/>
+  <dimension ref="A1:AA161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16636,6 +16636,564 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Hopsquared Wines &amp; Spirits Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Hopsquared Wines &amp; Spirits Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>121993</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Taichung</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Taichung City, Xitun District</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>50 Lane 301, Section 2, Henan Road</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hopsquared.com</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>hopsquared@gmail.com</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>+886 4 2452 1196</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>60269368</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr"/>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HopSquared</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_hopsquared_/</t>
+        </is>
+      </c>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr"/>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Wanshang International Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Wanshang International Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>54992</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>No. 17, Lane 107, Linsen North Road, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wanshang.com.tw</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>info@winebank.com.tw</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2523 3678</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>80489994</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr"/>
+      <c r="S157" s="2" t="inlineStr"/>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr"/>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Thirsty Scholar</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Thirsty Scholar</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>55003</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Taichung</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Taichung City, West District</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>172 Cunzhong Street</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>retail@thirsty-scholar.net</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>+886 4 2378 7546</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>42945705</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr"/>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thirstysc/</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thirsty_scholar_tw/</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr"/>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Danny Wine Collection Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Danny Wine Collection Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>55032</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>No. 22, Lane 69, Section 2, Jianguo South Road, Daan District</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dannycollection.com</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>dwc.taipei@gmail.com</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2708 8869</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>24755055</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr"/>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DannyWine</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dwc_taipei/</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr"/>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Wine O'clock Company Limited</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Wine O'clock Company Limited</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>55010</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>3 Yijiang Street</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>taiwan@wineoclock.com.tw</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2521 1860</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>82863813</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineOClockTaiwan/</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr"/>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Topcollection E.n. Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Topcollection E.n. Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>121872</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Kaohsiung</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Kaohsiung City, Gushan District</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>88 Meishu East 8th Street</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>topcollectionwine@gmail.com</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>+886 7 552 9782</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>59172984</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Topcollection.wine/</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Nicole Hu</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicole-hu-aa5929159/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA161"/>
+  <dimension ref="A1:AA165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17194,6 +17194,366 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Four Brothers Wine&amp;spirits International Ltd.</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Four Brothers Wine&amp;spirits International Ltd.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>145526</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Yonghe District</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>23 Lane 93, Section 1, Chenggong Road</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://wine97.blogspot.com</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>wine.spirits@msa.hinet.net</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2232 4199</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>24699126</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="2" t="inlineStr"/>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr"/>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>L' Etoile Vin L.t.d.</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>L' Etoile Vin L.t.d.</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>55207</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Songshan District</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>4 Lane 97, Section 4, Minsheng East Road</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>http://www.letoilevin.com, https://letoilevin.pixnet.net</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>etoile@letoilevin.com</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2547 3860</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>54353374</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr"/>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/letoIlevin/</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/etoilevin</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr"/>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Select Chile Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Select Chile Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>55215</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Da’an District</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>7 Lane 141, Section 1, Anhe Road</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chile.com.tw</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>service@chile.com.tw</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2755 6376</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>90137978</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/selectchile/</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr"/>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>C'est Le Vin Co.,ltd</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>C'est Le Vin Co.,ltd</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>55214</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Da’an District</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>18 Lane 31, Rui'an Street</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cestlevin.com.tw</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>contact@cestlevin.com.tw</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2700 3703</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>24943114</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cestlevin.tw/</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cestlevin.tw/</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr"/>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA165"/>
+  <dimension ref="A1:AA166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17554,6 +17554,99 @@
       <c r="Z165" s="2" t="inlineStr"/>
       <c r="AA165" s="2" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Dragons Lair Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Dragons Lair Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>145527</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Kaohsiung</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Kaohsiung City, Lingya District</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>1 Henan Road</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dlwine.cc</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>dragonsl@ms74.hinet.net</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>+886 4 2317 2929</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>16221752</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dlwine2016</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dragonslairwine/</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr"/>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA166"/>
+  <dimension ref="A1:AA168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17647,6 +17647,224 @@
       <c r="Z166" s="2" t="inlineStr"/>
       <c r="AA166" s="2" t="inlineStr"/>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>Travis Lin</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Buyer</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/travis-lin-58789710b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr"/>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>Sonia Chiou</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sonia-chiou-a6167641/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA168"/>
+  <dimension ref="A1:AA170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17865,6 +17865,224 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr"/>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Travis Lin</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Buyer</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/travis-lin-58789710b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr"/>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Sonia Chiou</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sonia-chiou-a6167641/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA170"/>
+  <dimension ref="A1:AA173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18083,6 +18083,293 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>VinoLife (醺活)</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr"/>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>168388</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>No. 6, Lane 191, Section 3, Minquan East Road, Songshan District</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://evening-wine.com</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Eveningwine2025@gmail.com</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2547 3895</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr"/>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr"/>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>Travis Lin</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Buyer</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/travis-lin-58789710b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>Sonia Chiou</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sonia-chiou-a6167641/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA173"/>
+  <dimension ref="A1:AA175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18370,6 +18370,224 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>Travis Lin</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Buyer</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/travis-lin-58789710b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>Sonia Chiou</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sonia-chiou-a6167641/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA175"/>
+  <dimension ref="A1:AA177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18588,6 +18588,224 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>Travis Lin</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Buyer</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/travis-lin-58789710b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Taiwan, Inc.</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>114842</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City, Xinzhuang District,</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>138 Jianguo 1st Road</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.costco.com.tw</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>yupeiyi69@gmail.com</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 449 9909</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>96972798</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TAIWAN.COSTCO/</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costco.taiwan/</t>
+        </is>
+      </c>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@costcotw1997</t>
+        </is>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>Sonia Chiou</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sonia-chiou-a6167641/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
